--- a/artfynd/A 62578-2025 artfynd.xlsx
+++ b/artfynd/A 62578-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>104731309</v>
       </c>
       <c r="B2" t="n">
-        <v>93132</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -716,10 +711,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>689114.7155859366</v>
+        <v>689115</v>
       </c>
       <c r="R2" t="n">
-        <v>6602791.37284532</v>
+        <v>6602791</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -792,15 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121417608</v>
+        <v>97730154</v>
       </c>
       <c r="B3" t="n">
-        <v>8436</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,42 +798,47 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Spåret, Spåret, Upl</t>
+          <t>Domarudden, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>689042</v>
+        <v>689113</v>
       </c>
       <c r="R3" t="n">
-        <v>6602686</v>
+        <v>6602720</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,22 +862,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2021-12-27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2021-12-27</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,15 +892,244 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>97730234</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Domarudden, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>689118</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6602726</v>
+      </c>
+      <c r="S4" t="n">
+        <v>12</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2021-12-27</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2021-12-27</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121417608</v>
+      </c>
+      <c r="B5" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Spåret, Spåret, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>689042</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6602686</v>
+      </c>
+      <c r="S5" t="n">
+        <v>15</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Tomas Fridström</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Tomas Fridström</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 62578-2025 artfynd.xlsx
+++ b/artfynd/A 62578-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
           <t>Nya Tärnan gruppen</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104731309</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -901,6 +911,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97730154</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1018,6 +1033,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97730234</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1130,8 +1150,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121417608</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>